--- a/data/trans_orig/IP18B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18B-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61731</t>
+          <t>62735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75667</t>
+          <t>76449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68611</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122375</t>
+          <t>122159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141395</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>26903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14084</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>66247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117068</t>
+          <t>117139</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133096</t>
+          <t>132866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28672</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>42253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>52597</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54168</t>
+          <t>53652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67560</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99684</t>
+          <t>100943</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117167</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36841</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18787</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118770</t>
+          <t>118840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137265</t>
+          <t>137118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125229</t>
+          <t>124666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143987</t>
+          <t>143468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251413</t>
+          <t>250075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276166</t>
+          <t>276497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23745</t>
+          <t>23986</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44813</t>
+          <t>44468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78777</t>
+          <t>79041</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>56340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69666</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>69220</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82431</t>
+          <t>82710</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>130199</t>
+          <t>130082</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>149155</t>
+          <t>148624</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49156</t>
+          <t>48974</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51003</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47384</t>
+          <t>46981</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57767</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88229</t>
+          <t>89387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105734</t>
+          <t>105874</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35788</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26091</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>24743</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>42525</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78823</t>
+          <t>83718</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>402162</t>
+          <t>403597</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>436091</t>
+          <t>436325</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>433225</t>
+          <t>431892</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>466783</t>
+          <t>466843</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>845859</t>
+          <t>845123</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>891827</t>
+          <t>891501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91836</t>
+          <t>92523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123009</t>
+          <t>121846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>97920</t>
+          <t>97363</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128881</t>
+          <t>127567</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>198923</t>
+          <t>197888</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>243162</t>
+          <t>241595</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>73569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>60542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73245</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126785</t>
+          <t>126693</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143783</t>
+          <t>144168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>16192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>30055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>80717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65155</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>77604</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>138325</t>
+          <t>137655</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154437</t>
+          <t>154427</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58843</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73257</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124339</t>
+          <t>124062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140498</t>
+          <t>140903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34122</t>
+          <t>33579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36367</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145658</t>
+          <t>144817</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163982</t>
+          <t>163836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156075</t>
+          <t>157044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>178222</t>
+          <t>176808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>308369</t>
+          <t>308746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>336008</t>
+          <t>336518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75626</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>98484</t>
+          <t>98770</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>114213</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92252</t>
+          <t>91448</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108428</t>
+          <t>108508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195380</t>
+          <t>195569</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>219833</t>
+          <t>219492</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>32580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61416</t>
+          <t>60614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27834</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46592</t>
+          <t>46611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58485</t>
+          <t>58662</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>78105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94281</t>
+          <t>94875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>23841</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41772</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>58858</t>
+          <t>58711</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64722</t>
+          <t>64853</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93370</t>
+          <t>93873</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>486191</t>
+          <t>487717</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>521018</t>
+          <t>521820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>509757</t>
+          <t>511278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>545117</t>
+          <t>547543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1010180</t>
+          <t>1008551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1058524</t>
+          <t>1059623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89469</t>
+          <t>87800</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119566</t>
+          <t>119295</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>91732</t>
+          <t>91078</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122000</t>
+          <t>121938</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>187670</t>
+          <t>184607</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>230773</t>
+          <t>230368</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53443</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>65663</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69595</t>
+          <t>68527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>81491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125695</t>
+          <t>126371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143546</t>
+          <t>143843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>16329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67806</t>
+          <t>67977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>82282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79211</t>
+          <t>79050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>137211</t>
+          <t>136834</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157297</t>
+          <t>157546</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>28965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48575</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36707</t>
+          <t>37199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47065</t>
+          <t>47566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>41603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83435</t>
+          <t>83017</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99652</t>
+          <t>98818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32997</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144455</t>
+          <t>145867</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164878</t>
+          <t>165158</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119463</t>
+          <t>120011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141273</t>
+          <t>141036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270472</t>
+          <t>271160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>300418</t>
+          <t>302037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33623</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51966</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>34450</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74120</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101188</t>
+          <t>100114</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>88078</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103798</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92002</t>
+          <t>92227</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108755</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>186555</t>
+          <t>186616</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208564</t>
+          <t>209966</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>33499</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>58422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43548</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50353</t>
+          <t>50376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73259</t>
+          <t>73480</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90170</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,5%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37613</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37059</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30113</t>
+          <t>30335</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50478</t>
+          <t>52112</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>54337</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81303</t>
+          <t>82347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>450835</t>
+          <t>451194</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>486052</t>
+          <t>486069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>453701</t>
+          <t>453907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>492314</t>
+          <t>489461</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>915068</t>
+          <t>914347</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>967112</t>
+          <t>967099</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>104758</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>138194</t>
+          <t>138045</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>112863</t>
+          <t>114265</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>147706</t>
+          <t>149280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>230692</t>
+          <t>228536</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>278114</t>
+          <t>275493</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21691</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>25292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9036</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8125</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63911</t>
+          <t>63646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43213</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>31,84%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>83,45%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>18403</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>69534</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83245</t>
+          <t>83118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84993</t>
+          <t>85128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>104178</t>
+          <t>103807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>159296</t>
+          <t>160187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>182378</t>
+          <t>183871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15986</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>15348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24289</t>
+          <t>22692</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44365</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
